--- a/files/programming-tasks/programmieraufgaben_linden.xlsx
+++ b/files/programming-tasks/programmieraufgaben_linden.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164D7A69-A978-4599-98B9-D5E01201A892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E28522-0DE6-4152-A3E8-21D640F94348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="90" windowWidth="25860" windowHeight="20805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -421,6 +421,48 @@
 if __name__ == '__main__':
     unittest.main()
 </t>
+  </si>
+  <si>
+    <t>testClassName</t>
+  </si>
+  <si>
+    <t>runMethod</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>warmkalt</t>
+  </si>
+  <si>
+    <t>2000, 5</t>
+  </si>
+  <si>
+    <t>rabattiere</t>
+  </si>
+  <si>
+    <t>sternchen</t>
+  </si>
+  <si>
+    <t>wetter</t>
+  </si>
+  <si>
+    <t>nutzername</t>
+  </si>
+  <si>
+    <t>"Stern"</t>
+  </si>
+  <si>
+    <t>Jan', 'Lee'</t>
+  </si>
+  <si>
+    <t>entferne</t>
+  </si>
+  <si>
+    <t>"Katze", 3</t>
+  </si>
+  <si>
+    <t>test_main.py</t>
   </si>
 </sst>
 </file>
@@ -514,7 +556,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -580,6 +622,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -885,7 +931,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -896,10 +942,11 @@
     <col min="8" max="8" width="105.5703125" style="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="33.5703125" customWidth="1"/>
+    <col min="12" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -930,8 +977,17 @@
       <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -962,8 +1018,17 @@
       <c r="J2" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -994,8 +1059,17 @@
       <c r="J3" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1026,8 +1100,17 @@
       <c r="J4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="393" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="393" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -1058,8 +1141,17 @@
       <c r="J5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -1090,8 +1182,17 @@
       <c r="J6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1122,8 +1223,17 @@
       <c r="J7" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1133,7 +1243,7 @@
       <c r="H8" s="15"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -1143,7 +1253,7 @@
       <c r="H9" s="15"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1153,7 +1263,7 @@
       <c r="H10" s="15"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1163,7 +1273,7 @@
       <c r="H11" s="15"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1173,7 +1283,7 @@
       <c r="H12" s="15"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1183,7 +1293,7 @@
       <c r="H13" s="15"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1193,7 +1303,7 @@
       <c r="H14" s="15"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -1203,7 +1313,7 @@
       <c r="H15" s="20"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>

--- a/files/programming-tasks/programmieraufgaben_linden.xlsx
+++ b/files/programming-tasks/programmieraufgaben_linden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E28522-0DE6-4152-A3E8-21D640F94348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE30C066-B272-4112-8F1B-FC09A5069AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="240" windowWidth="45150" windowHeight="20505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="61">
   <si>
     <t>id</t>
   </si>
@@ -73,9 +73,6 @@
   <si>
     <t>def warmkalt(temp):
     # Deine Lösung</t>
-  </si>
-  <si>
-    <t>1. Wie warm ist es?</t>
   </si>
   <si>
     <t>2. RABATT AUF ALLES</t>
@@ -119,188 +116,14 @@
     <t>6. Schokolade ohne k</t>
   </si>
   <si>
-    <t>&lt;p&gt;Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zur&amp;uuml;ckgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also&lt;br&gt;&lt;em&gt;rauswerfen(&amp;quot;schokolade&amp;quot;, 4)&lt;/em&gt;&lt;br&gt;soll &amp;quot;schoolade&amp;quot; zur&amp;uuml;ckgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t>entferne.py</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zurückgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>rauswerfen("schokolade", 4)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-soll "schoolade" zurückgeben.
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Schreibe eine Funktion </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>warmkalt(temp)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, die eine Zahl als Parameter erhält und einen String zurückgibt. Wenn die Temperatur unter 18 Grad liegt, soll „Es ist sehr kalt!“ zurückgegeben werden. Wenn die Temperatur über 25 Grad liegt, soll „Es ist sehr warm!“ zurückgegeben werden. Ansonsten soll „Es ist angenehm!“ Zurückgegeben werden.
-</t>
-    </r>
-  </si>
-  <si>
-    <t>&lt;p&gt;Schreibe eine Funktion &lt;em&gt;warmkalt(temp)&lt;/em&gt;, die eine Zahl als Parameter erh&amp;auml;lt und einen String zur&amp;uuml;ckgibt. Wenn die Temperatur unter 18 Grad liegt, soll &amp;bdquo;Es ist sehr kalt!&amp;ldquo; zur&amp;uuml;ckgegeben werden. Wenn die Temperatur &amp;uuml;ber 25 Grad liegt, soll &amp;bdquo;Es ist sehr warm!&amp;ldquo; zur&amp;uuml;ckgegeben werden. Ansonsten soll &amp;bdquo;Es ist angenehm!&amp;ldquo; Zur&amp;uuml;ckgegeben werden.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Strings sind Aneinanderreihungen von Buchstaben. Ihr habt sie schon benutzt! Sie stehen immer in einfachen oder doppelten Anführungszeichen. 
-Es gibt verschiedene Möglichkeiten in python, Strings zu manipulieren. Zum Beispiel kann man mit dem '+' - Operator mehrere Strings zu einem kombinieren.
-Beispiel:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">string1 = "Hallo "
-string2 = "Welt"
-print(string1+string2) # gibt "Hallo Welt" aus
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Schreibe eine Funktion sternchen(wort), die ein * vor und hinter dem Wort hinzufügt und den resultierenden String zurückgibt!
-Also sternchen('bling') soll '*bling*' zurückgeben.</t>
-    </r>
-  </si>
-  <si>
     <t>&lt;p&gt;Strings sind Aneinanderreihungen von Buchstaben. Ihr habt sie schon benutzt! Sie stehen immer in einfachen oder doppelten Anf&amp;uuml;hrungszeichen.&lt;br&gt;Es gibt verschiedene M&amp;ouml;glichkeiten in python, Strings zu manipulieren. Zum Beispiel kann man mit dem &amp;apos;+&amp;apos; - Operator mehrere Strings zu einem kombinieren.&lt;br&gt;&lt;br&gt;Beispiel:&lt;br&gt;&lt;em&gt;string1 = &amp;quot;Hallo &amp;quot;&lt;br&gt;string2 = &amp;quot;Welt&amp;quot;&lt;br&gt;print(string1+string2) # gibt &amp;quot;Hallo Welt&amp;quot; aus&lt;/em&gt;&lt;br&gt;&lt;br&gt;Schreibe eine Funktion sternchen(wort), die ein * vor und hinter dem Wort hinzuf&amp;uuml;gt und den resultierenden String zur&amp;uuml;ckgibt!&lt;br&gt;Also &lt;em&gt;sternchen(&amp;apos;bling&amp;apos;)&lt;/em&gt; soll &amp;apos;*bling*&amp;apos; zur&amp;uuml;ckgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ein Kaufhaus hat überall für den Ausverkauf überall Rabatt-Schilder angeklebt, aber nicht den entgültigen Preis ausgerechnet. Der findige Informatiker oder die findige Informatikerin hat dafür aber eine Lösung!
-Schreibe eine Funktion </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rabattiere(preis, rabatt)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, die eine Preis in Euro und einen Rabatt in Prozent erhält und den Rabatt auf den Originalpreis anwendet. Der rabattierte Preis soll zurückgegeben werden.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100</t>
-    </r>
   </si>
   <si>
     <t>&lt;p&gt;Ein Kaufhaus hat &amp;uuml;berall f&amp;uuml;r den Ausverkauf &amp;uuml;berall Rabatt-Schilder angeklebt, aber nicht den entg&amp;uuml;ltigen Preis ausgerechnet. Der findige Informatiker oder die findige Informatikerin hat daf&amp;uuml;r aber eine L&amp;ouml;sung!&lt;br&gt;Schreibe eine Funktion rabattiere(preis, rabatt), die eine Preis in Euro und einen Rabatt in Prozent erh&amp;auml;lt und den Rabatt auf den Originalpreis anwendet. Der rabattierte Preis soll zur&amp;uuml;ckgegeben werden.&lt;/p&gt;
 &lt;p&gt;&lt;br&gt;Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100&lt;/p&gt;</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Strings verhalten sich in python in vielerlei Hinsicht wie Listen. Wir können zum Beispiel wie bei Listen mit eckigen Klammern auf einzelne Buchstaben oder Teile eines Strings zugreifen.
-Der Benutzername eines Schülers auf der Schul-Website besteht immer aus den ersten drei Buchstaben des Vornamens und den ersten drei Buchstaben des Nachnamens, getrennt durch einen Punkt (alles in Kleinbuchstaben). Also der Benutzername von Alfred Mustermann wäre alf.mus .
-Erstellen eine Funktion </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>nutzername(vorname, nachname)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, die den Benutzernamen als String zurückgibt!
-Tipp: Mit der Funktion </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">lower() </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>kannst du einen String in Kleinbuchstaben umwandeln!</t>
-    </r>
   </si>
   <si>
     <t>&lt;p&gt;Strings verhalten sich in python in vielerlei Hinsicht wie Listen. Wir k&amp;ouml;nnen zum Beispiel wie bei Listen mit eckigen Klammern auf einzelne Buchstaben oder Teile eines Strings zugreifen.&lt;/p&gt;
@@ -315,20 +138,6 @@
   </si>
   <si>
     <t>python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">import unittest
-from warmkalt import warmkalt
-class TestWarmKalt(unittest.TestCase):
-    def test_sehr_kalt(self):
-        self.assertEqual(warmkalt(10), "Es ist sehr kalt!")
-    def test_angenehm(self):
-        self.assertEqual(warmkalt(20), "Es ist angenehm!")
-    def test_sehr_warm(self):
-        self.assertEqual(warmkalt(30), "Es ist sehr warm!")
-if __name__ == '__main__':
-    unittest.main()
-</t>
   </si>
   <si>
     <t xml:space="preserve">import unittest
@@ -432,9 +241,6 @@
     <t>input</t>
   </si>
   <si>
-    <t>warmkalt</t>
-  </si>
-  <si>
     <t>2000, 5</t>
   </si>
   <si>
@@ -453,9 +259,6 @@
     <t>"Stern"</t>
   </si>
   <si>
-    <t>Jan', 'Lee'</t>
-  </si>
-  <si>
     <t>entferne</t>
   </si>
   <si>
@@ -463,13 +266,65 @@
   </si>
   <si>
     <t>test_main.py</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>gut</t>
+  </si>
+  <si>
+    <t>überprüft nicht alle Listeneinträge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  File "&lt;string&gt;", line 1
+    import nutzername; nutzername.nutzername(Jan', 'Lee'),
+                                                       ^
+SyntaxError: unterminated string literal (detected at line 1)
+</t>
+  </si>
+  <si>
+    <t>Hier steht einmal entferne und einmal rauswerfen als Funktionsname. Es funktioniert nur mit entferne.</t>
+  </si>
+  <si>
+    <t>Strings sind Aneinanderreihungen von Buchstaben. Ihr habt sie schon benutzt! Sie stehen immer in einfachen oder doppelten Anführungszeichen. 
+Es gibt verschiedene Möglichkeiten in python, Strings zu manipulieren. Zum Beispiel kann man mit dem '+' - Operator mehrere Strings zu einem kombinieren.
+Beispiel:
+string1 = "Hallo "
+string2 = "Welt"
+print(string1+string2) # gibt "Hallo Welt" aus
+Schreibe eine Funktion sternchen(wort), die ein * vor und hinter dem Wort hinzufügt und den resultierenden String zurückgibt!
+Also sternchen('bling') soll '*bling*' zurückgeben.</t>
+  </si>
+  <si>
+    <t>Ein Kaufhaus hat überall für den Ausverkauf überall Rabatt-Schilder angeklebt, aber nicht den entgültigen Preis ausgerechnet. Der findige Informatiker oder die findige Informatikerin hat dafür aber eine Lösung!
+Schreibe eine Funktion rabattiere(preis, rabatt), die eine Preis in Euro und einen Rabatt in Prozent erhält und den Rabatt auf den Originalpreis anwendet. Der rabattierte Preis soll zurückgegeben werden.
+Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zur&amp;uuml;ckgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also&lt;br&gt;&lt;em&gt;entferne(&amp;quot;schokolade&amp;quot;, 4)&lt;/em&gt;&lt;br&gt;soll &amp;quot;schoolade&amp;quot; zur&amp;uuml;ckgeben.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zurückgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also
+entferne("schokolade", 4)
+soll "schoolade" zurückgeben.
+</t>
+  </si>
+  <si>
+    <t>"Jan", "Lee"</t>
+  </si>
+  <si>
+    <t>Strings verhalten sich in python in vielerlei Hinsicht wie Listen. Wir können zum Beispiel wie bei Listen mit eckigen Klammern auf einzelne Buchstaben oder Teile eines Strings zugreifen.
+Der Benutzername eines Schülers auf der Schul-Website besteht immer aus den ersten drei Buchstaben des Vornamens und den ersten drei Buchstaben des Nachnamens, getrennt durch einen Punkt (alles in Kleinbuchstaben). Also der Benutzername von Alfred Mustermann wäre alf.mus .
+Erstellen eine Funktion nutzername(vorname, nachname), die den Benutzernamen als String zurückgibt!
+Tipp: Mit der Funktion lower() kannst du einen String in Kleinbuchstaben umwandeln!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,39 +357,24 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -553,10 +393,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -574,9 +415,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -586,18 +424,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -616,18 +442,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Gut" xfId="1" builtinId="26"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -931,22 +781,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.5703125" style="1" customWidth="1"/>
     <col min="5" max="5" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="66.140625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="105.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="105.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="33.5703125" customWidth="1"/>
-    <col min="12" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="115.85546875" customWidth="1"/>
+    <col min="15" max="16" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -954,21 +806,21 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="14" t="s">
         <v>13</v>
       </c>
       <c r="I1" t="s">
@@ -977,350 +829,337 @@
       <c r="J1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="23" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="17">
+        <v>23</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="17">
+        <v>0</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="23" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>3</v>
+      </c>
+      <c r="B3" s="17">
+        <v>1</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="17">
+        <v>9</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="22">
+        <v>0</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="23" customFormat="1" ht="393" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>4</v>
+      </c>
+      <c r="B4" s="17">
+        <v>1</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="17">
+        <v>19</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="22">
+        <v>0</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="23">
+        <v>2</v>
+      </c>
+      <c r="N4" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="23" customFormat="1" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>5</v>
+      </c>
+      <c r="B5" s="17">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="17">
+        <v>25</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="22">
+        <v>0</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="25" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24">
+        <v>6</v>
+      </c>
+      <c r="B6" s="24">
+        <v>1</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="24">
+        <v>9</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="24">
+        <v>0</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="M1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="7">
-        <v>19</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="7">
-        <v>23</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>1</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="7">
-        <v>9</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="1">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="393" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7">
-        <v>1</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="7">
-        <v>19</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N6" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="M5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>1</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="7">
-        <v>25</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M6" s="24" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="2" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="4">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="10"/>
+      <c r="J7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="F8" s="16"/>
+      <c r="F8" s="11"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="15"/>
+      <c r="H8" s="10"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
-      <c r="F9" s="16"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="15"/>
+      <c r="H9" s="10"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="F10" s="16"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="15"/>
+      <c r="H10" s="10"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
-      <c r="F11" s="16"/>
+      <c r="F11" s="11"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="10"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="F12" s="16"/>
+      <c r="F12" s="11"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="15"/>
+      <c r="H12" s="10"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
-      <c r="F13" s="16"/>
+      <c r="F13" s="11"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="10"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="8"/>
       <c r="H14" s="15"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="20"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="15"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:13" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="20"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="15"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1328,9 +1167,10 @@
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="20"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="6"/>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1338,10 +1178,9 @@
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
-      <c r="F18" s="16"/>
+      <c r="F18" s="11"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="6"/>
+      <c r="H18" s="10"/>
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1349,40 +1188,41 @@
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
-      <c r="F19" s="16"/>
+      <c r="F19" s="11"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="10"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="F20" s="16"/>
+    <row r="20" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="13"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="15"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="18"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="F21" s="11"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="8"/>
+      <c r="H21" s="10"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
-      <c r="F22" s="16"/>
+      <c r="F22" s="11"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="6"/>
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1390,9 +1230,9 @@
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="F23" s="16"/>
+      <c r="F23" s="11"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="15"/>
+      <c r="H23" s="10"/>
       <c r="I23" s="6"/>
       <c r="J23" s="4"/>
     </row>
@@ -1401,9 +1241,9 @@
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
-      <c r="F24" s="16"/>
+      <c r="F24" s="11"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="15"/>
+      <c r="H24" s="10"/>
       <c r="I24" s="6"/>
       <c r="J24" s="4"/>
     </row>
@@ -1412,9 +1252,9 @@
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
-      <c r="F25" s="16"/>
+      <c r="F25" s="11"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="15"/>
+      <c r="H25" s="10"/>
       <c r="I25" s="6"/>
       <c r="J25" s="4"/>
     </row>
@@ -1423,9 +1263,9 @@
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="F26" s="16"/>
+      <c r="F26" s="11"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="15"/>
+      <c r="H26" s="10"/>
       <c r="I26" s="6"/>
       <c r="J26" s="4"/>
     </row>
@@ -1434,9 +1274,9 @@
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
-      <c r="F27" s="16"/>
+      <c r="F27" s="11"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="15"/>
+      <c r="H27" s="10"/>
       <c r="I27" s="6"/>
       <c r="J27" s="4"/>
     </row>
@@ -1445,22 +1285,11 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
-      <c r="F28" s="16"/>
+      <c r="F28" s="11"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="15"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="6"/>
       <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1544,7 +1373,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -1558,7 +1387,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -1572,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>6</v>

--- a/files/programming-tasks/programmieraufgaben_linden.xlsx
+++ b/files/programming-tasks/programmieraufgaben_linden.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\hefl\files\programming-tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE30C066-B272-4112-8F1B-FC09A5069AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A5ED54-7403-4391-B8B0-C1BC0220010A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="240" windowWidth="45150" windowHeight="20505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="90" windowWidth="25875" windowHeight="20805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aufgaben" sheetId="1" r:id="rId1"/>
@@ -85,10 +85,6 @@
   </si>
   <si>
     <t>wetter.py</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;Bei Rollenspielen wie Dungeons &amp;amp; Dragons muss der Spielleiter h&amp;auml;ufig das Wetter f&amp;uuml;r den aktuellen Tag festlegen. Daf&amp;uuml;r nutzt er normalerweise eine nummerierte Liste und einen W&amp;uuml;rfel.&lt;br&gt;Erstellen eine Funktion wetter(zahl), die eine gew&amp;uuml;rfelte Zahl entgegennimmt und ein Wetter ausgibt! Nimm an, dass der W&amp;uuml;rfel acht Seiten hat, also die Zahlen von 1 bis 8 gew&amp;uuml;rfelt werden k&amp;ouml;nnen. Hier ist die Liste aus dem Buch:&lt;/p&gt;
-&lt;p&gt;&lt;br&gt;1 Starker Regen&lt;br&gt;2 Sonne&lt;br&gt;3 Sonne&lt;br&gt;4 Wolken&lt;br&gt;5 Sturm&lt;br&gt;6 Nieselregen&lt;br&gt;7 Hagel&lt;br&gt;8 Nebel&lt;br&gt;&lt;br&gt;Nutze f&amp;uuml;r die Speicherung der Wetter eine Liste. Falls die Zahl die &amp;uuml;bergeben wurde nicht zwischen 1 und 8 liegt, soll &amp;quot;Unbekanntes Wetter&amp;quot; zur&amp;uuml;ckgegeben werden.&lt;br&gt;&lt;br&gt;Beispiel:&lt;br&gt;&lt;em&gt;print(wetter(5) )&lt;/em&gt;&lt;br&gt;soll &amp;quot;Sturm&amp;quot; ausgeben.&lt;/p&gt;</t>
   </si>
   <si>
     <t>Bei Rollenspielen wie Dungeons &amp; Dragons muss der Spielleiter häufig das Wetter für den aktuellen Tag festlegen. Dafür nutzt er normalerweise eine nummerierte Liste und einen Würfel.
@@ -117,18 +113,6 @@
   </si>
   <si>
     <t>entferne.py</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;Strings sind Aneinanderreihungen von Buchstaben. Ihr habt sie schon benutzt! Sie stehen immer in einfachen oder doppelten Anf&amp;uuml;hrungszeichen.&lt;br&gt;Es gibt verschiedene M&amp;ouml;glichkeiten in python, Strings zu manipulieren. Zum Beispiel kann man mit dem &amp;apos;+&amp;apos; - Operator mehrere Strings zu einem kombinieren.&lt;br&gt;&lt;br&gt;Beispiel:&lt;br&gt;&lt;em&gt;string1 = &amp;quot;Hallo &amp;quot;&lt;br&gt;string2 = &amp;quot;Welt&amp;quot;&lt;br&gt;print(string1+string2) # gibt &amp;quot;Hallo Welt&amp;quot; aus&lt;/em&gt;&lt;br&gt;&lt;br&gt;Schreibe eine Funktion sternchen(wort), die ein * vor und hinter dem Wort hinzuf&amp;uuml;gt und den resultierenden String zur&amp;uuml;ckgibt!&lt;br&gt;Also &lt;em&gt;sternchen(&amp;apos;bling&amp;apos;)&lt;/em&gt; soll &amp;apos;*bling*&amp;apos; zur&amp;uuml;ckgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;Ein Kaufhaus hat &amp;uuml;berall f&amp;uuml;r den Ausverkauf &amp;uuml;berall Rabatt-Schilder angeklebt, aber nicht den entg&amp;uuml;ltigen Preis ausgerechnet. Der findige Informatiker oder die findige Informatikerin hat daf&amp;uuml;r aber eine L&amp;ouml;sung!&lt;br&gt;Schreibe eine Funktion rabattiere(preis, rabatt), die eine Preis in Euro und einen Rabatt in Prozent erh&amp;auml;lt und den Rabatt auf den Originalpreis anwendet. Der rabattierte Preis soll zur&amp;uuml;ckgegeben werden.&lt;/p&gt;
-&lt;p&gt;&lt;br&gt;Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>&lt;p&gt;Strings verhalten sich in python in vielerlei Hinsicht wie Listen. Wir k&amp;ouml;nnen zum Beispiel wie bei Listen mit eckigen Klammern auf einzelne Buchstaben oder Teile eines Strings zugreifen.&lt;/p&gt;
-&lt;p&gt;Der Benutzername eines Sch&amp;uuml;lers auf der Schul-Website besteht immer aus den ersten drei Buchstaben des Vornamens und den ersten drei Buchstaben des Nachnamens, getrennt durch einen Punkt (alles in Kleinbuchstaben). Also der Benutzername von Alfred Mustermann w&amp;auml;re alf.mus .&lt;/p&gt;
-&lt;p&gt;&lt;br&gt;Erstellen eine Funktion &lt;em&gt;nutzername(vorname, nachname)&lt;/em&gt;, die den Benutzernamen als String zur&amp;uuml;ckgibt!&lt;br&gt;&lt;br&gt;Tipp: Mit der Funktion&lt;em&gt;&amp;nbsp;lower()&lt;/em&gt; kannst du einen String in Kleinbuchstaben umwandeln!&lt;/p&gt;</t>
   </si>
   <si>
     <t>Programming_Language</t>
@@ -302,9 +286,6 @@
 Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100</t>
   </si>
   <si>
-    <t>&lt;p&gt;Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zur&amp;uuml;ckgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also&lt;br&gt;&lt;em&gt;entferne(&amp;quot;schokolade&amp;quot;, 4)&lt;/em&gt;&lt;br&gt;soll &amp;quot;schoolade&amp;quot; zur&amp;uuml;ckgeben.&lt;/p&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Schreibe eine Funktion entferne(wort, index). Die Funktion soll das Wort zurückgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also
 entferne("schokolade", 4)
 soll "schoolade" zurückgeben.
@@ -318,6 +299,47 @@
 Der Benutzername eines Schülers auf der Schul-Website besteht immer aus den ersten drei Buchstaben des Vornamens und den ersten drei Buchstaben des Nachnamens, getrennt durch einen Punkt (alles in Kleinbuchstaben). Also der Benutzername von Alfred Mustermann wäre alf.mus .
 Erstellen eine Funktion nutzername(vorname, nachname), die den Benutzernamen als String zurückgibt!
 Tipp: Mit der Funktion lower() kannst du einen String in Kleinbuchstaben umwandeln!</t>
+  </si>
+  <si>
+    <t>Ein Kaufhaus hat überall für den Ausverkauf überall Rabatt-Schilder angeklebt, aber nicht den endgültigen Preis ausgerechnet. Der findige Informatiker oder die findige Informatikerin hat dafür aber eine Lösung!  
+Schreibe eine Funktion `rabattiere(preis, rabatt)`, die eine Preis in Euro und einen Rabatt in Prozent erhält und den Rabatt auf den Originalpreis anwendet. Der rabattierte Preis soll zurückgegeben werden.
+Tipp: rabattierter Preis = Originalpreis - Originalpreis*Rabatt in Prozent /100</t>
+  </si>
+  <si>
+    <t>Strings sind Aneinanderreihungen von Buchstaben. Ihr habt sie schon benutzt! Sie stehen immer in einfachen oder doppelten Anführungszeichen. Es gibt verschiedene Möglichkeiten in Python, Strings zu manipulieren. Zum Beispiel kann man mit dem '+' - Operator mehrere Strings zu einem kombinieren.
+Beispiel:  
+*string1 = "Hallo "*  
+*string2 = "Welt"*  
+*print(string1+string2)* # gibt "Hallo Welt" aus
+Schreibe eine Funktion `sternchen(wort)`, die ein * vor und hinter dem Wort hinzufügt und den resultierenden String zurückgibt!  
+Also `sternchen('bling')` soll '*bling*' zurückgeben.</t>
+  </si>
+  <si>
+    <t>Bei Rollenspielen wie Dungeons &amp; Dragons muss der Spielleiter häufig das Wetter für den aktuellen Tag festlegen. Dafür nutzt er normalerweise eine nummerierte Liste und einen Würfel.
+Erstellen eine Funktion `wetter(zahl)`, die eine gewürfelte Zahl entgegennimmt und ein Wetter ausgibt! Nimm an, dass der Würfel acht Seiten hat, also die Zahlen von 1 bis 8 gewürfelt werden können. Hier ist die Liste aus dem Buch:
+1. Starker Regen  
+2. Sonne  
+3. Sonne  
+4. Wolken  
+5. Sturm  
+6. Nieselregen  
+7. Hagel  
+8. Nebel  
+Nutze für die Speicherung der Wetter eine Liste. Falls die Zahl die übergeben wurde nicht zwischen 1 und 8 liegt, soll "Unbekanntes Wetter" zurückgegeben werden.
+Beispiel:  
+* `print(wetter(5))`  
+  soll "Sturm" ausgeben.</t>
+  </si>
+  <si>
+    <t>Strings verhalten sich in Python in vielerlei Hinsicht wie Listen. Wir können zum Beispiel wie bei Listen mit eckigen Klammern auf einzelne Buchstaben oder Teile eines Strings zugreifen.
+Der Benutzername eines Schülers auf der Schul-Website besteht immer aus den ersten drei Buchstaben des Vornamens und den ersten drei Buchstaben des Nachnamens, getrennt durch einen Punkt (alles in Kleinbuchstaben). Also der Benutzername von Alfred Mustermann wäre alf.mus.
+Erstellen eine Funktion *nutzername(vorname, nachname)*, die den Benutzernamen als String zurückgibt!
+Tipp: Mit der Funktion *lower()* kannst du einen String in Kleinbuchstaben umwandeln!</t>
+  </si>
+  <si>
+    <t>Schreibe eine Funktion `entferne(wort, index)`. Die Funktion soll das Wort zurückgeben, bei dem an der Stelle von Index der Buchstabe entfernt wurde. Also
+*entferne("schokolade", 4)*
+soll "schoolade" zurückgeben.</t>
   </si>
 </sst>
 </file>
@@ -806,10 +828,10 @@
         <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -830,16 +852,16 @@
         <v>15</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="23" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -850,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D2" s="17">
         <v>23</v>
@@ -859,13 +881,13 @@
         <v>17</v>
       </c>
       <c r="F2" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
         <v>56</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>28</v>
       </c>
       <c r="I2" s="23" t="s">
         <v>5</v>
@@ -874,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="K2" s="23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M2" s="23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N2" s="23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="23" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -894,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D3" s="17">
         <v>9</v>
@@ -903,13 +925,13 @@
         <v>18</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
       </c>
       <c r="I3" s="19" t="s">
         <v>7</v>
@@ -918,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L3" s="23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="23" customFormat="1" ht="393" customHeight="1" x14ac:dyDescent="0.25">
@@ -938,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D4" s="17">
         <v>19</v>
@@ -947,13 +969,13 @@
         <v>19</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>21</v>
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>58</v>
       </c>
       <c r="I4" s="27" t="s">
         <v>20</v>
@@ -962,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M4" s="23">
         <v>2</v>
       </c>
       <c r="N4" s="23" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="23" customFormat="1" ht="202.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -982,40 +1004,40 @@
         <v>1</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D5" s="17">
         <v>25</v>
       </c>
       <c r="E5" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>23</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>24</v>
       </c>
       <c r="J5" s="22">
         <v>0</v>
       </c>
       <c r="K5" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="25" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="25" customFormat="1" ht="141" customHeight="1" x14ac:dyDescent="0.25">
@@ -1026,40 +1048,40 @@
         <v>1</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D6" s="24">
         <v>9</v>
       </c>
       <c r="E6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="25" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>26</v>
       </c>
       <c r="J6" s="24">
         <v>0</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1387,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -1401,7 +1423,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>6</v>
